--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.80486066085636</v>
+        <v>5.493289857389158</v>
       </c>
       <c r="D2" t="n">
-        <v>34.87370051437503</v>
+        <v>5.666976333585943</v>
       </c>
       <c r="E2" t="n">
-        <v>18.24786985066012</v>
+        <v>2.965278850732269</v>
       </c>
       <c r="F2" t="n">
-        <v>17.36700030235898</v>
+        <v>2.822137549133335</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.447197634602948</v>
+        <v>0.722669615622979</v>
       </c>
       <c r="D3" t="n">
-        <v>6.308589484253048</v>
+        <v>1.02514579119112</v>
       </c>
       <c r="E3" t="n">
-        <v>18.24786985066012</v>
+        <v>2.965278850732269</v>
       </c>
       <c r="F3" t="n">
-        <v>17.36700030235898</v>
+        <v>2.822137549133335</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.31553256278542</v>
+        <v>7.851274041452632</v>
       </c>
       <c r="D4" t="n">
-        <v>47.89101627441751</v>
+        <v>7.782290144592846</v>
       </c>
       <c r="E4" t="n">
-        <v>18.24786985066012</v>
+        <v>2.965278850732269</v>
       </c>
       <c r="F4" t="n">
-        <v>17.36700030235898</v>
+        <v>2.822137549133335</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
